--- a/safety_test_result1­V1_20260323_222948.xlsx
+++ b/safety_test_result1­V1_20260323_222948.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hilla\source\repos\ucanrr_safety_eval_api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCD22B70-8E1F-4D0B-8E35-4DC579F36DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A70E5A3-A6E4-49F4-95F4-DD2DCBF6F0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18165" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{D4F6F4FD-2DF6-4F70-8DEE-F6CE6BE1E4FF}"/>
   </bookViews>
@@ -5406,6 +5406,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1A3D971-CF41-4003-8801-6C23FEDCDE52}">
   <dimension ref="A1:Z536"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="11" max="11" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="219.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="255.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
